--- a/h100price/data/a100_rental_prices.xlsx
+++ b/h100price/data/a100_rental_prices.xlsx
@@ -82898,6 +82898,7702 @@
         </is>
       </c>
     </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:10Z</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1121">
+        <v>2.054406</v>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1121">
+        <v>1</v>
+      </c>
+      <c r="K1121">
+        <v>2.054406</v>
+      </c>
+      <c r="L1121">
+        <v>2.054406</v>
+      </c>
+      <c r="M1121" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1121" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1121" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652321,"reliability":0.9978637,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:10Z</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1122">
+        <v>3.737037</v>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1122">
+        <v>2</v>
+      </c>
+      <c r="K1122">
+        <v>1.868519</v>
+      </c>
+      <c r="L1122">
+        <v>1.868519</v>
+      </c>
+      <c r="M1122" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1122" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1122" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795433,"reliability":0.980312,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:10Z</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1123">
+        <v>4.107331</v>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1123">
+        <v>2</v>
+      </c>
+      <c r="K1123">
+        <v>2.053666</v>
+      </c>
+      <c r="L1123">
+        <v>2.053666</v>
+      </c>
+      <c r="M1123" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1123" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1123" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652330,"reliability":0.9978637,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:10Z</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1124">
+        <v>4.268889</v>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1124">
+        <v>4</v>
+      </c>
+      <c r="K1124">
+        <v>1.067222</v>
+      </c>
+      <c r="L1124">
+        <v>1.067222</v>
+      </c>
+      <c r="M1124" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1124" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1124" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":32289337,"reliability":0.9992809,"location":"Germany, DE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>20260529T181010Z</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:10:10Z</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1125">
+        <v>7.47037</v>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1125">
+        <v>4</v>
+      </c>
+      <c r="K1125">
+        <v>1.867593</v>
+      </c>
+      <c r="L1125">
+        <v>1.867593</v>
+      </c>
+      <c r="M1125" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1125" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1125" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1125" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795430,"reliability":0.980312,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1126">
+        <v>0.762053</v>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1126">
+        <v>1</v>
+      </c>
+      <c r="K1126">
+        <v>0.762053</v>
+      </c>
+      <c r="L1126">
+        <v>0.762053</v>
+      </c>
+      <c r="M1126" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1126" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1126" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1126" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38432948,"reliability":0.9969164,"location":"The Netherlands, NL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1127">
+        <v>0.843704</v>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1127">
+        <v>1</v>
+      </c>
+      <c r="K1127">
+        <v>0.843704</v>
+      </c>
+      <c r="L1127">
+        <v>0.843704</v>
+      </c>
+      <c r="M1127" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1127" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1127" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1127" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38391714,"reliability":0.9700024,"location":"Texas, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1128">
+        <v>1.137037</v>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1128">
+        <v>1</v>
+      </c>
+      <c r="K1128">
+        <v>1.137037</v>
+      </c>
+      <c r="L1128">
+        <v>1.137037</v>
+      </c>
+      <c r="M1128" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1128" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1128" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1128" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37310465,"reliability":0.9769904,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1129">
+        <v>1.189333</v>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1129">
+        <v>1</v>
+      </c>
+      <c r="K1129">
+        <v>1.189333</v>
+      </c>
+      <c r="L1129">
+        <v>1.189333</v>
+      </c>
+      <c r="M1129" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1129" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1129" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1129" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34475477,"reliability":0.9718174,"location":"Czechia, CZ"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1130">
+        <v>1.32</v>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1130">
+        <v>1</v>
+      </c>
+      <c r="K1130">
+        <v>1.32</v>
+      </c>
+      <c r="L1130">
+        <v>1.32</v>
+      </c>
+      <c r="M1130" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1130" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1130" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453409,"reliability":0.9972008,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1131">
+        <v>1.874215</v>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1131">
+        <v>1</v>
+      </c>
+      <c r="K1131">
+        <v>1.874215</v>
+      </c>
+      <c r="L1131">
+        <v>1.874215</v>
+      </c>
+      <c r="M1131" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1131" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1131" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1131" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":28181268,"reliability":0.9957172,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1132">
+        <v>1.940634</v>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1132">
+        <v>1</v>
+      </c>
+      <c r="K1132">
+        <v>1.940634</v>
+      </c>
+      <c r="L1132">
+        <v>1.940634</v>
+      </c>
+      <c r="M1132" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1132" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1132" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652357,"reliability":0.996702,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1133">
+        <v>3.069333</v>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1133">
+        <v>2</v>
+      </c>
+      <c r="K1133">
+        <v>1.534667</v>
+      </c>
+      <c r="L1133">
+        <v>1.534667</v>
+      </c>
+      <c r="M1133" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1133" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1133" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38187139,"reliability":0.9954809,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1134">
+        <v>3.737037</v>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1134">
+        <v>2</v>
+      </c>
+      <c r="K1134">
+        <v>1.868519</v>
+      </c>
+      <c r="L1134">
+        <v>1.868519</v>
+      </c>
+      <c r="M1134" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1134" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1134" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1134" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795429,"reliability":0.9804054,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1135">
+        <v>3.846818</v>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1135">
+        <v>2</v>
+      </c>
+      <c r="K1135">
+        <v>1.923409</v>
+      </c>
+      <c r="L1135">
+        <v>1.923409</v>
+      </c>
+      <c r="M1135" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1135" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1135" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1135" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307928,"reliability":0.9954404,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1136">
+        <v>4.268889</v>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1136">
+        <v>4</v>
+      </c>
+      <c r="K1136">
+        <v>1.067222</v>
+      </c>
+      <c r="L1136">
+        <v>1.067222</v>
+      </c>
+      <c r="M1136" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1136" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1136" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":32289337,"reliability":0.9992812,"location":"Germany, DE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1137">
+        <v>4.537037</v>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1137">
+        <v>4</v>
+      </c>
+      <c r="K1137">
+        <v>1.134259</v>
+      </c>
+      <c r="L1137">
+        <v>1.134259</v>
+      </c>
+      <c r="M1137" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1137" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1137" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1137" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":28497576,"reliability":0.9865574,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1138">
+        <v>7.47037</v>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1138">
+        <v>4</v>
+      </c>
+      <c r="K1138">
+        <v>1.867593</v>
+      </c>
+      <c r="L1138">
+        <v>1.867593</v>
+      </c>
+      <c r="M1138" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1138" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1138" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1138" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795430,"reliability":0.9804054,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1139">
+        <v>8.002222</v>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1139">
+        <v>2</v>
+      </c>
+      <c r="K1139">
+        <v>4.001111</v>
+      </c>
+      <c r="L1139">
+        <v>4.001111</v>
+      </c>
+      <c r="M1139" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1139" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1139" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1139" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.8701443,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1140">
+        <v>8.413764</v>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1140">
+        <v>4</v>
+      </c>
+      <c r="K1140">
+        <v>2.103441</v>
+      </c>
+      <c r="L1140">
+        <v>2.103441</v>
+      </c>
+      <c r="M1140" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1140" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1140" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1140" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27479301,"reliability":0.9960944,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>20260529T191321Z</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:13:22Z</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x8</t>
+        </is>
+      </c>
+      <c r="G1141">
+        <v>12.268889</v>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1141">
+        <v>8</v>
+      </c>
+      <c r="K1141">
+        <v>1.533611</v>
+      </c>
+      <c r="L1141">
+        <v>1.533611</v>
+      </c>
+      <c r="M1141" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1141" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1141" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1141" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37922231,"reliability":0.9997339,"location":"Minnesota, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1142">
+        <v>0.668889</v>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1142">
+        <v>1</v>
+      </c>
+      <c r="K1142">
+        <v>0.668889</v>
+      </c>
+      <c r="L1142">
+        <v>0.668889</v>
+      </c>
+      <c r="M1142" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1142" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1142" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37715178,"reliability":0.9886999,"location":"California, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1143">
+        <v>0.843704</v>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1143">
+        <v>1</v>
+      </c>
+      <c r="K1143">
+        <v>0.843704</v>
+      </c>
+      <c r="L1143">
+        <v>0.843704</v>
+      </c>
+      <c r="M1143" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1143" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1143" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1143" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38391714,"reliability":0.9709716,"location":"Texas, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1144">
+        <v>1.135556</v>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1144">
+        <v>1</v>
+      </c>
+      <c r="K1144">
+        <v>1.135556</v>
+      </c>
+      <c r="L1144">
+        <v>1.135556</v>
+      </c>
+      <c r="M1144" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1144" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1144" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36939660,"reliability":0.9825568,"location":"Sweden, SE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1145">
+        <v>1.32</v>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1145">
+        <v>1</v>
+      </c>
+      <c r="K1145">
+        <v>1.32</v>
+      </c>
+      <c r="L1145">
+        <v>1.32</v>
+      </c>
+      <c r="M1145" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1145" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1145" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1145" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453414,"reliability":0.9972008,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1146">
+        <v>1.92415</v>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1146">
+        <v>1</v>
+      </c>
+      <c r="K1146">
+        <v>1.92415</v>
+      </c>
+      <c r="L1146">
+        <v>1.92415</v>
+      </c>
+      <c r="M1146" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1146" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1146" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1146" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307932,"reliability":0.9954404,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1147">
+        <v>1.93141</v>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1147">
+        <v>1</v>
+      </c>
+      <c r="K1147">
+        <v>1.93141</v>
+      </c>
+      <c r="L1147">
+        <v>1.93141</v>
+      </c>
+      <c r="M1147" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1147" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1147" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1147" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652304,"reliability":0.9950805,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1148">
+        <v>3.069333</v>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1148">
+        <v>2</v>
+      </c>
+      <c r="K1148">
+        <v>1.534667</v>
+      </c>
+      <c r="L1148">
+        <v>1.534667</v>
+      </c>
+      <c r="M1148" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1148" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1148" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1148" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38187139,"reliability":0.9954874,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1149">
+        <v>3.737037</v>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1149">
+        <v>2</v>
+      </c>
+      <c r="K1149">
+        <v>1.868519</v>
+      </c>
+      <c r="L1149">
+        <v>1.868519</v>
+      </c>
+      <c r="M1149" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1149" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1149" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1149" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795429,"reliability":0.9804999,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1150">
+        <v>3.846818</v>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1150">
+        <v>2</v>
+      </c>
+      <c r="K1150">
+        <v>1.923409</v>
+      </c>
+      <c r="L1150">
+        <v>1.923409</v>
+      </c>
+      <c r="M1150" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1150" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1150" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1150" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307928,"reliability":0.9954404,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1151">
+        <v>4.268889</v>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1151">
+        <v>4</v>
+      </c>
+      <c r="K1151">
+        <v>1.067222</v>
+      </c>
+      <c r="L1151">
+        <v>1.067222</v>
+      </c>
+      <c r="M1151" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1151" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1151" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1151" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":32289337,"reliability":0.9992812,"location":"Germany, DE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1152">
+        <v>4.537037</v>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1152">
+        <v>4</v>
+      </c>
+      <c r="K1152">
+        <v>1.134259</v>
+      </c>
+      <c r="L1152">
+        <v>1.134259</v>
+      </c>
+      <c r="M1152" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1152" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1152" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1152" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":28497576,"reliability":0.9865574,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1153">
+        <v>7.47037</v>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1153">
+        <v>4</v>
+      </c>
+      <c r="K1153">
+        <v>1.867593</v>
+      </c>
+      <c r="L1153">
+        <v>1.867593</v>
+      </c>
+      <c r="M1153" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1153" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1153" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1153" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795430,"reliability":0.9804999,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1154">
+        <v>8.002222</v>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1154">
+        <v>2</v>
+      </c>
+      <c r="K1154">
+        <v>4.001111</v>
+      </c>
+      <c r="L1154">
+        <v>4.001111</v>
+      </c>
+      <c r="M1154" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1154" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1154" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1154" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.8902151,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1155">
+        <v>8.413764</v>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1155">
+        <v>4</v>
+      </c>
+      <c r="K1155">
+        <v>2.103441</v>
+      </c>
+      <c r="L1155">
+        <v>2.103441</v>
+      </c>
+      <c r="M1155" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1155" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1155" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1155" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27479301,"reliability":0.9960944,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>20260529T191709Z</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>2026-05-29T19:17:09Z</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x8</t>
+        </is>
+      </c>
+      <c r="G1156">
+        <v>12.268889</v>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1156">
+        <v>8</v>
+      </c>
+      <c r="K1156">
+        <v>1.533611</v>
+      </c>
+      <c r="L1156">
+        <v>1.533611</v>
+      </c>
+      <c r="M1156" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1156" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1156" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1156" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37922231,"reliability":0.9997339,"location":"Minnesota, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1157">
+        <v>0.734815</v>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1157">
+        <v>1</v>
+      </c>
+      <c r="K1157">
+        <v>0.734815</v>
+      </c>
+      <c r="L1157">
+        <v>0.734815</v>
+      </c>
+      <c r="M1157" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1157" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1157" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1157" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":35422824,"reliability":0.9969641,"location":"Slovenia, SI"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1158">
+        <v>1.205333</v>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1158">
+        <v>1</v>
+      </c>
+      <c r="K1158">
+        <v>1.205333</v>
+      </c>
+      <c r="L1158">
+        <v>1.205333</v>
+      </c>
+      <c r="M1158" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1158" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1158" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1158" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453407,"reliability":0.9972085,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1159">
+        <v>2.026385</v>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1159">
+        <v>1</v>
+      </c>
+      <c r="K1159">
+        <v>2.026385</v>
+      </c>
+      <c r="L1159">
+        <v>2.026385</v>
+      </c>
+      <c r="M1159" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1159" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1159" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1159" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26396256,"reliability":0.9978128,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1160">
+        <v>2.052981</v>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1160">
+        <v>1</v>
+      </c>
+      <c r="K1160">
+        <v>2.052981</v>
+      </c>
+      <c r="L1160">
+        <v>2.052981</v>
+      </c>
+      <c r="M1160" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1160" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1160" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1160" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26216739,"reliability":0.9967037,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1161">
+        <v>2.408</v>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1161">
+        <v>2</v>
+      </c>
+      <c r="K1161">
+        <v>1.204</v>
+      </c>
+      <c r="L1161">
+        <v>1.204</v>
+      </c>
+      <c r="M1161" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1161" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1161" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1161" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453405,"reliability":0.9972085,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1162">
+        <v>3.069333</v>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1162">
+        <v>2</v>
+      </c>
+      <c r="K1162">
+        <v>1.534667</v>
+      </c>
+      <c r="L1162">
+        <v>1.534667</v>
+      </c>
+      <c r="M1162" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1162" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1162" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1162" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38187139,"reliability":0.9954937,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1163">
+        <v>3.737037</v>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1163">
+        <v>2</v>
+      </c>
+      <c r="K1163">
+        <v>1.868519</v>
+      </c>
+      <c r="L1163">
+        <v>1.868519</v>
+      </c>
+      <c r="M1163" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1163" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1163" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1163" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795429,"reliability":0.9805963,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1164">
+        <v>7.47037</v>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1164">
+        <v>4</v>
+      </c>
+      <c r="K1164">
+        <v>1.867593</v>
+      </c>
+      <c r="L1164">
+        <v>1.867593</v>
+      </c>
+      <c r="M1164" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1164" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1164" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1164" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795430,"reliability":0.9805963,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>20260529T202242Z</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>2026-05-29T20:22:42Z</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1165">
+        <v>8.002222</v>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1165">
+        <v>2</v>
+      </c>
+      <c r="K1165">
+        <v>4.001111</v>
+      </c>
+      <c r="L1165">
+        <v>4.001111</v>
+      </c>
+      <c r="M1165" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1165" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1165" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1165" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.9463641,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1166">
+        <v>0.668889</v>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1166">
+        <v>1</v>
+      </c>
+      <c r="K1166">
+        <v>0.668889</v>
+      </c>
+      <c r="L1166">
+        <v>0.668889</v>
+      </c>
+      <c r="M1166" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1166" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1166" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1166" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37715178,"reliability":0.9887381,"location":"California, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1167">
+        <v>1.001481</v>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1167">
+        <v>1</v>
+      </c>
+      <c r="K1167">
+        <v>1.001481</v>
+      </c>
+      <c r="L1167">
+        <v>1.001481</v>
+      </c>
+      <c r="M1167" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1167" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1167" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1167" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36449293,"reliability":0.9689197,"location":"Czechia, CZ"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1168">
+        <v>1.001481</v>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1168">
+        <v>1</v>
+      </c>
+      <c r="K1168">
+        <v>1.001481</v>
+      </c>
+      <c r="L1168">
+        <v>1.001481</v>
+      </c>
+      <c r="M1168" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1168" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1168" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1168" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":30895670,"reliability":0.9989416,"location":"Czechia, CZ"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1169">
+        <v>1.137037</v>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1169">
+        <v>1</v>
+      </c>
+      <c r="K1169">
+        <v>1.137037</v>
+      </c>
+      <c r="L1169">
+        <v>1.137037</v>
+      </c>
+      <c r="M1169" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1169" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1169" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1169" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37298527,"reliability":0.9279754,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1170">
+        <v>1.137037</v>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1170">
+        <v>1</v>
+      </c>
+      <c r="K1170">
+        <v>1.137037</v>
+      </c>
+      <c r="L1170">
+        <v>1.137037</v>
+      </c>
+      <c r="M1170" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1170" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1170" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1170" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":30907658,"reliability":0.9924521,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1171">
+        <v>1.141481</v>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1171">
+        <v>1</v>
+      </c>
+      <c r="K1171">
+        <v>1.141481</v>
+      </c>
+      <c r="L1171">
+        <v>1.141481</v>
+      </c>
+      <c r="M1171" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1171" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1171" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1171" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375273,"reliability":0.5115,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1172">
+        <v>1.205333</v>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1172">
+        <v>1</v>
+      </c>
+      <c r="K1172">
+        <v>1.205333</v>
+      </c>
+      <c r="L1172">
+        <v>1.205333</v>
+      </c>
+      <c r="M1172" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1172" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1172" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1172" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453407,"reliability":0.9972085,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1173">
+        <v>1.937936</v>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1173">
+        <v>1</v>
+      </c>
+      <c r="K1173">
+        <v>1.937936</v>
+      </c>
+      <c r="L1173">
+        <v>1.937936</v>
+      </c>
+      <c r="M1173" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1173" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1173" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1173" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27666235,"reliability":0.9929238,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1174">
+        <v>2.026385</v>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1174">
+        <v>1</v>
+      </c>
+      <c r="K1174">
+        <v>2.026385</v>
+      </c>
+      <c r="L1174">
+        <v>2.026385</v>
+      </c>
+      <c r="M1174" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1174" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1174" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1174" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26396262,"reliability":0.9978128,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1175">
+        <v>2.27037</v>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1175">
+        <v>2</v>
+      </c>
+      <c r="K1175">
+        <v>1.135185</v>
+      </c>
+      <c r="L1175">
+        <v>1.135185</v>
+      </c>
+      <c r="M1175" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1175" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1175" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1175" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37298525,"reliability":0.9279754,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1176">
+        <v>2.281481</v>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1176">
+        <v>2</v>
+      </c>
+      <c r="K1176">
+        <v>1.140741</v>
+      </c>
+      <c r="L1176">
+        <v>1.140741</v>
+      </c>
+      <c r="M1176" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1176" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1176" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1176" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375274,"reliability":0.5115,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1177">
+        <v>3.737037</v>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1177">
+        <v>2</v>
+      </c>
+      <c r="K1177">
+        <v>1.868519</v>
+      </c>
+      <c r="L1177">
+        <v>1.868519</v>
+      </c>
+      <c r="M1177" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1177" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1177" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1177" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795429,"reliability":0.9805963,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1178">
+        <v>4.051289</v>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1178">
+        <v>2</v>
+      </c>
+      <c r="K1178">
+        <v>2.025644</v>
+      </c>
+      <c r="L1178">
+        <v>2.025644</v>
+      </c>
+      <c r="M1178" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1178" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1178" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1178" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26396258,"reliability":0.9978128,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1179">
+        <v>4.104481</v>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1179">
+        <v>2</v>
+      </c>
+      <c r="K1179">
+        <v>2.05224</v>
+      </c>
+      <c r="L1179">
+        <v>2.05224</v>
+      </c>
+      <c r="M1179" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1179" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1179" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1179" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26216731,"reliability":0.9967037,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1180">
+        <v>4.537037</v>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1180">
+        <v>4</v>
+      </c>
+      <c r="K1180">
+        <v>1.134259</v>
+      </c>
+      <c r="L1180">
+        <v>1.134259</v>
+      </c>
+      <c r="M1180" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1180" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1180" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1180" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":28497576,"reliability":0.9866291,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1181">
+        <v>7.47037</v>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1181">
+        <v>4</v>
+      </c>
+      <c r="K1181">
+        <v>1.867593</v>
+      </c>
+      <c r="L1181">
+        <v>1.867593</v>
+      </c>
+      <c r="M1181" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1181" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1181" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1181" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37795430,"reliability":0.9805963,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1182">
+        <v>8.002222</v>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1182">
+        <v>2</v>
+      </c>
+      <c r="K1182">
+        <v>4.001111</v>
+      </c>
+      <c r="L1182">
+        <v>4.001111</v>
+      </c>
+      <c r="M1182" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1182" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1182" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1182" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.9463641,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>20260529T210557Z</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>2026-05-29T21:05:58Z</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x8</t>
+        </is>
+      </c>
+      <c r="G1183">
+        <v>12.268889</v>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1183">
+        <v>8</v>
+      </c>
+      <c r="K1183">
+        <v>1.533611</v>
+      </c>
+      <c r="L1183">
+        <v>1.533611</v>
+      </c>
+      <c r="M1183" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1183" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1183" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1183" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37922231,"reliability":0.9997339,"location":"Minnesota, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1184">
+        <v>1.137037</v>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1184">
+        <v>1</v>
+      </c>
+      <c r="K1184">
+        <v>1.137037</v>
+      </c>
+      <c r="L1184">
+        <v>1.137037</v>
+      </c>
+      <c r="M1184" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1184" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1184" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1184" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37310465,"reliability":0.9779157,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1185">
+        <v>1.137037</v>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1185">
+        <v>1</v>
+      </c>
+      <c r="K1185">
+        <v>1.137037</v>
+      </c>
+      <c r="L1185">
+        <v>1.137037</v>
+      </c>
+      <c r="M1185" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1185" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1185" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1185" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37298527,"reliability":0.9803562,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1186">
+        <v>1.137037</v>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1186">
+        <v>1</v>
+      </c>
+      <c r="K1186">
+        <v>1.137037</v>
+      </c>
+      <c r="L1186">
+        <v>1.137037</v>
+      </c>
+      <c r="M1186" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1186" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1186" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1186" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":30907658,"reliability":0.9925721,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1187">
+        <v>1.268148</v>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1187">
+        <v>1</v>
+      </c>
+      <c r="K1187">
+        <v>1.268148</v>
+      </c>
+      <c r="L1187">
+        <v>1.268148</v>
+      </c>
+      <c r="M1187" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1187" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1187" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1187" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375275,"reliability":0.6389235,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1188">
+        <v>1.535579</v>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1188">
+        <v>1</v>
+      </c>
+      <c r="K1188">
+        <v>1.535579</v>
+      </c>
+      <c r="L1188">
+        <v>1.535579</v>
+      </c>
+      <c r="M1188" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1188" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1188" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1188" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":35122393,"reliability":0.9963567,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1189">
+        <v>1.917114</v>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1189">
+        <v>1</v>
+      </c>
+      <c r="K1189">
+        <v>1.917114</v>
+      </c>
+      <c r="L1189">
+        <v>1.917114</v>
+      </c>
+      <c r="M1189" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1189" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1189" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1189" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307904,"reliability":0.9969491,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1190">
+        <v>1.93141</v>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1190">
+        <v>1</v>
+      </c>
+      <c r="K1190">
+        <v>1.93141</v>
+      </c>
+      <c r="L1190">
+        <v>1.93141</v>
+      </c>
+      <c r="M1190" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1190" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1190" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1190" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652309,"reliability":0.9951045,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1191">
+        <v>2.534815</v>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1191">
+        <v>2</v>
+      </c>
+      <c r="K1191">
+        <v>1.267407</v>
+      </c>
+      <c r="L1191">
+        <v>1.267407</v>
+      </c>
+      <c r="M1191" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1191" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1191" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1191" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375274,"reliability":0.6389235,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1192">
+        <v>3.832747</v>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1192">
+        <v>2</v>
+      </c>
+      <c r="K1192">
+        <v>1.916373</v>
+      </c>
+      <c r="L1192">
+        <v>1.916373</v>
+      </c>
+      <c r="M1192" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1192" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1192" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1192" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307896,"reliability":0.9969491,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1193">
+        <v>4.051289</v>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1193">
+        <v>2</v>
+      </c>
+      <c r="K1193">
+        <v>2.025644</v>
+      </c>
+      <c r="L1193">
+        <v>2.025644</v>
+      </c>
+      <c r="M1193" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1193" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1193" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1193" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26396258,"reliability":0.9978168,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1194">
+        <v>8.002222</v>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1194">
+        <v>2</v>
+      </c>
+      <c r="K1194">
+        <v>4.001111</v>
+      </c>
+      <c r="L1194">
+        <v>4.001111</v>
+      </c>
+      <c r="M1194" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1194" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1194" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1194" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.9558033,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>20260530T004718Z</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>2026-05-30T00:47:19Z</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1195">
+        <v>8.20748</v>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1195">
+        <v>4</v>
+      </c>
+      <c r="K1195">
+        <v>2.05187</v>
+      </c>
+      <c r="L1195">
+        <v>2.05187</v>
+      </c>
+      <c r="M1195" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1195" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1195" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1195" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26216733,"reliability":0.9967144,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1196">
+        <v>1.137037</v>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1196">
+        <v>1</v>
+      </c>
+      <c r="K1196">
+        <v>1.137037</v>
+      </c>
+      <c r="L1196">
+        <v>1.137037</v>
+      </c>
+      <c r="M1196" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1196" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1196" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1196" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37310463,"reliability":0.9779157,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1197">
+        <v>1.204913</v>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1197">
+        <v>1</v>
+      </c>
+      <c r="K1197">
+        <v>1.204913</v>
+      </c>
+      <c r="L1197">
+        <v>1.204913</v>
+      </c>
+      <c r="M1197" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1197" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1197" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1197" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34453414,"reliability":0.9972319,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1198">
+        <v>1.268148</v>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1198">
+        <v>1</v>
+      </c>
+      <c r="K1198">
+        <v>1.268148</v>
+      </c>
+      <c r="L1198">
+        <v>1.268148</v>
+      </c>
+      <c r="M1198" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1198" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1198" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1198" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375273,"reliability":0.6389235,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1199">
+        <v>1.268148</v>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1199">
+        <v>1</v>
+      </c>
+      <c r="K1199">
+        <v>1.268148</v>
+      </c>
+      <c r="L1199">
+        <v>1.268148</v>
+      </c>
+      <c r="M1199" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1199" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1199" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1199" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":34619630,"reliability":0.9967692,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1200">
+        <v>1.917114</v>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1200">
+        <v>1</v>
+      </c>
+      <c r="K1200">
+        <v>1.917114</v>
+      </c>
+      <c r="L1200">
+        <v>1.917114</v>
+      </c>
+      <c r="M1200" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1200" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1200" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1200" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307899,"reliability":0.9969491,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1201">
+        <v>1.940634</v>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1201">
+        <v>1</v>
+      </c>
+      <c r="K1201">
+        <v>1.940634</v>
+      </c>
+      <c r="L1201">
+        <v>1.940634</v>
+      </c>
+      <c r="M1201" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1201" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1201" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1201" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652350,"reliability":0.9967151,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1202">
+        <v>2.534815</v>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1202">
+        <v>2</v>
+      </c>
+      <c r="K1202">
+        <v>1.267407</v>
+      </c>
+      <c r="L1202">
+        <v>1.267407</v>
+      </c>
+      <c r="M1202" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1202" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1202" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1202" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375274,"reliability":0.6389235,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1203">
+        <v>3.068913</v>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1203">
+        <v>2</v>
+      </c>
+      <c r="K1203">
+        <v>1.534456</v>
+      </c>
+      <c r="L1203">
+        <v>1.534456</v>
+      </c>
+      <c r="M1203" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1203" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1203" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1203" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38187137,"reliability":0.9955186,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1204">
+        <v>3.846818</v>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1204">
+        <v>2</v>
+      </c>
+      <c r="K1204">
+        <v>1.923409</v>
+      </c>
+      <c r="L1204">
+        <v>1.923409</v>
+      </c>
+      <c r="M1204" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1204" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1204" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1204" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307928,"reliability":0.9954637,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1205">
+        <v>4.051289</v>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1205">
+        <v>2</v>
+      </c>
+      <c r="K1205">
+        <v>2.025644</v>
+      </c>
+      <c r="L1205">
+        <v>2.025644</v>
+      </c>
+      <c r="M1205" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1205" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1205" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1205" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26396258,"reliability":0.9978168,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1206">
+        <v>7.664012</v>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1206">
+        <v>4</v>
+      </c>
+      <c r="K1206">
+        <v>1.916003</v>
+      </c>
+      <c r="L1206">
+        <v>1.916003</v>
+      </c>
+      <c r="M1206" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1206" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1206" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1206" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307898,"reliability":0.9969491,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>20260530T005959Z</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1207">
+        <v>8.002222</v>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1207">
+        <v>2</v>
+      </c>
+      <c r="K1207">
+        <v>4.001111</v>
+      </c>
+      <c r="L1207">
+        <v>4.001111</v>
+      </c>
+      <c r="M1207" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1207" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1207" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1207" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137194,"reliability":0.9558033,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1208">
+        <v>0.695111</v>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1208">
+        <v>1</v>
+      </c>
+      <c r="K1208">
+        <v>0.695111</v>
+      </c>
+      <c r="L1208">
+        <v>0.695111</v>
+      </c>
+      <c r="M1208" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1208" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1208" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1208" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37127280,"reliability":0.8505937,"location":"California, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1209">
+        <v>0.695111</v>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1209">
+        <v>1</v>
+      </c>
+      <c r="K1209">
+        <v>0.695111</v>
+      </c>
+      <c r="L1209">
+        <v>0.695111</v>
+      </c>
+      <c r="M1209" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1209" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1209" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1209" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37474261,"reliability":0.8479393,"location":"California, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>A100 PCIE x1</t>
+        </is>
+      </c>
+      <c r="G1210">
+        <v>0.868148</v>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1210">
+        <v>1</v>
+      </c>
+      <c r="K1210">
+        <v>0.868148</v>
+      </c>
+      <c r="L1210">
+        <v>0.868148</v>
+      </c>
+      <c r="M1210" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1210" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1210" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1210" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":25139281,"reliability":0.997287,"location":"Virginia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1211">
+        <v>1.001481</v>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1211">
+        <v>1</v>
+      </c>
+      <c r="K1211">
+        <v>1.001481</v>
+      </c>
+      <c r="L1211">
+        <v>1.001481</v>
+      </c>
+      <c r="M1211" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1211" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1211" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1211" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36449296,"reliability":0.9701911,"location":"Czechia, CZ"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1212">
+        <v>1.135556</v>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1212">
+        <v>1</v>
+      </c>
+      <c r="K1212">
+        <v>1.135556</v>
+      </c>
+      <c r="L1212">
+        <v>1.135556</v>
+      </c>
+      <c r="M1212" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1212" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1212" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1212" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36939663,"reliability":0.9825842,"location":"Sweden, SE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1213">
+        <v>1.137037</v>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1213">
+        <v>1</v>
+      </c>
+      <c r="K1213">
+        <v>1.137037</v>
+      </c>
+      <c r="L1213">
+        <v>1.137037</v>
+      </c>
+      <c r="M1213" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1213" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1213" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1213" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":37310453,"reliability":0.978201,"location":"Georgia, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1214">
+        <v>1.268148</v>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1214">
+        <v>1</v>
+      </c>
+      <c r="K1214">
+        <v>1.268148</v>
+      </c>
+      <c r="L1214">
+        <v>1.268148</v>
+      </c>
+      <c r="M1214" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1214" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1214" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1214" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375273,"reliability":0.6813307,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1215">
+        <v>1.87037</v>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1215">
+        <v>2</v>
+      </c>
+      <c r="K1215">
+        <v>0.935185</v>
+      </c>
+      <c r="L1215">
+        <v>0.935185</v>
+      </c>
+      <c r="M1215" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1215" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1215" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1215" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":29202322,"reliability":0.9962935,"location":"Estonia, EE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1216">
+        <v>1.940634</v>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1216">
+        <v>1</v>
+      </c>
+      <c r="K1216">
+        <v>1.940634</v>
+      </c>
+      <c r="L1216">
+        <v>1.940634</v>
+      </c>
+      <c r="M1216" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1216" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1216" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1216" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652350,"reliability":0.9967202,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x1</t>
+        </is>
+      </c>
+      <c r="G1217">
+        <v>2.054406</v>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1217">
+        <v>1</v>
+      </c>
+      <c r="K1217">
+        <v>2.054406</v>
+      </c>
+      <c r="L1217">
+        <v>2.054406</v>
+      </c>
+      <c r="M1217" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1217" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1217" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1217" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27652321,"reliability":0.9978689,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1218">
+        <v>2.268889</v>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1218">
+        <v>2</v>
+      </c>
+      <c r="K1218">
+        <v>1.134444</v>
+      </c>
+      <c r="L1218">
+        <v>1.134444</v>
+      </c>
+      <c r="M1218" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1218" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1218" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1218" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":36939650,"reliability":0.9825842,"location":"Sweden, SE"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1219">
+        <v>2.534815</v>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1219">
+        <v>2</v>
+      </c>
+      <c r="K1219">
+        <v>1.267407</v>
+      </c>
+      <c r="L1219">
+        <v>1.267407</v>
+      </c>
+      <c r="M1219" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1219" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1219" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1219" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38375274,"reliability":0.6813307,"location":"United Kingdom, GB"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>A100 PCIE x2</t>
+        </is>
+      </c>
+      <c r="G1220">
+        <v>3.068913</v>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1220">
+        <v>2</v>
+      </c>
+      <c r="K1220">
+        <v>1.534456</v>
+      </c>
+      <c r="L1220">
+        <v>1.534456</v>
+      </c>
+      <c r="M1220" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1220" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1220" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1220" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38187137,"reliability":0.9955304,"location":"Japan, JP"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1221">
+        <v>3.832747</v>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1221">
+        <v>2</v>
+      </c>
+      <c r="K1221">
+        <v>1.916373</v>
+      </c>
+      <c r="L1221">
+        <v>1.916373</v>
+      </c>
+      <c r="M1221" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1221" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1221" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1221" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":26307900,"reliability":0.9969564,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x2</t>
+        </is>
+      </c>
+      <c r="G1222">
+        <v>8.002222</v>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1222">
+        <v>2</v>
+      </c>
+      <c r="K1222">
+        <v>4.001111</v>
+      </c>
+      <c r="L1222">
+        <v>4.001111</v>
+      </c>
+      <c r="M1222" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1222" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1222" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1222" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137196,"reliability":0.956078,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1223">
+        <v>8.413764</v>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1223">
+        <v>4</v>
+      </c>
+      <c r="K1223">
+        <v>2.103441</v>
+      </c>
+      <c r="L1223">
+        <v>2.103441</v>
+      </c>
+      <c r="M1223" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1223" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1223" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1223" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":27479301,"reliability":0.9961208,"location":"Massachusetts, US"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>20260530T023249Z</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>2026-05-30T02:32:50Z</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Vast.ai</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>A100</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>rental</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>A100 SXM4 x4</t>
+        </is>
+      </c>
+      <c r="G1224">
+        <v>16.002222</v>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>instance_hour</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1224">
+        <v>4</v>
+      </c>
+      <c r="K1224">
+        <v>4.000556</v>
+      </c>
+      <c r="L1224">
+        <v>4.000556</v>
+      </c>
+      <c r="M1224" t="inlineStr">
+        <is>
+          <t>on-demand marketplace</t>
+        </is>
+      </c>
+      <c r="N1224" t="inlineStr">
+        <is>
+          <t>rentable</t>
+        </is>
+      </c>
+      <c r="O1224" t="inlineStr">
+        <is>
+          <t>https://cloud.vast.ai/create/</t>
+        </is>
+      </c>
+      <c r="P1224" t="inlineStr">
+        <is>
+          <t>{"basis":"official bundles API","offerId":38137195,"reliability":0.956078,"location":"France, FR"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>